--- a/docs/downloads/经营分_津河省区__津西北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__津西北片区_2026-10-18.xlsx
@@ -1141,7 +1141,7 @@
         <v>82</v>
       </c>
       <c r="I7" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1647,29 +1647,29 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7054677357143001128</t>
+          <t>6876418317968574479</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>天津大学五大道锦江都城酒店</t>
+          <t>喆啡酒店（天津西站天津之眼复兴路地铁站店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>锦江都城(天津大学总医院五大道店)</t>
+          <t>喆啡酒店(天津西站北广场卓朗科技发展店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>87</v>
       </c>
       <c r="I13" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1689,13 +1689,13 @@
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1728,20 +1728,24 @@
           <t>津西北片区</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6667085073147283469</t>
+          <t>7054677357143001128</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津西站人民医院地铁站店</t>
+          <t>天津大学五大道锦江都城酒店</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津西站人民医院地铁站店)</t>
+          <t>锦江都城(天津大学总医院五大道店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1753,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1773,13 +1777,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1812,24 +1816,20 @@
           <t>津西北片区</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601140755148851204</t>
+          <t>6667085073147283469</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7天优品（天津鼓楼地铁站大悦城店）</t>
+          <t>麗枫酒店·天津西站人民医院地铁站店</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7天优品(天津鼓楼地铁站大悦城店)</t>
+          <t>麗枫酒店(天津西站人民医院地铁站店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1907,17 +1907,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601137242222118916</t>
+          <t>6601140755148851204</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>锦江之星（天津西站咸阳路地铁站店）</t>
+          <t>7天优品（天津鼓楼地铁站大悦城店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>锦江之星(天津长江道店)</t>
+          <t>7天优品(天津鼓楼地铁站大悦城店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1929,7 +1929,7 @@
         <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1995,17 +1995,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6876418317968574479</t>
+          <t>6962005731608397861</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津西站天津之眼复兴路地铁站店）</t>
+          <t>喆啡酒店（天津鞍山西道地铁站店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津西站北广场卓朗科技发展店)</t>
+          <t>喆啡酒店(天津鞍山西道地铁站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2083,17 +2083,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6962005731608397861</t>
+          <t>6856745426805147648</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津鞍山西道地铁站店）</t>
+          <t>维也纳酒店（天津奥体中心天塔店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津鞍山西道地铁站店)</t>
+          <t>维也纳酒店(天津奥体中心天塔店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2105,7 +2105,7 @@
         <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2125,13 +2125,13 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2171,29 +2171,29 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6856745426805147648</t>
+          <t>7002795464235960356</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津奥体中心天塔店）</t>
+          <t>麗枫酒店·天津奥体中心店</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津奥体中心天塔店)</t>
+          <t>麗枫酒店(天津奥体中心店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H19" t="n">
         <v>92</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2213,13 +2213,13 @@
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2259,17 +2259,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7002795464235960356</t>
+          <t>6702573180134885388</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津奥体中心店</t>
+          <t>麗枫酒店·天津西站湘潭道店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津奥体中心店)</t>
+          <t>麗枫酒店(天津西站湘潭道店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2281,7 +2281,7 @@
         <v>92</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2347,17 +2347,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6702573180134885388</t>
+          <t>6601137242222118916</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津西站湘潭道店</t>
+          <t>锦江之星（天津西站咸阳路地铁站店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津西站湘潭道店)</t>
+          <t>锦江之星(天津长江道店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
